--- a/www/ig/fhir/annuaire/1.2.0-snapshot-1/StructureDefinition-as-ext-organization-budget-type.xlsx
+++ b/www/ig/fhir/annuaire/1.2.0-snapshot-1/StructureDefinition-as-ext-organization-budget-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-1</t>
+    <t>1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:13:23+00:00</t>
+    <t>2026-06-19T14:20:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/ig/fhir/annuaire/1.2.0-snapshot-1/StructureDefinition-as-ext-organization-budget-type.xlsx
+++ b/www/ig/fhir/annuaire/1.2.0-snapshot-1/StructureDefinition-as-ext-organization-budget-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-2</t>
+    <t>1.2.0-snapshot-1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:20:56+00:00</t>
+    <t>2026-06-16T14:13:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
